--- a/assets/templates/s29-blank.xlsx
+++ b/assets/templates/s29-blank.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\Филимонова\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EB08BE8-6B02-4693-99BC-298F07DCD44D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{724A6343-8D33-440A-A4C9-924BFA3BC9B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{ECB51198-8F26-4281-85AE-3DB1B3DC9F05}"/>
   </bookViews>
@@ -18,38 +18,38 @@
   <definedNames>
     <definedName name="docGro" localSheetId="0">'С-29'!$A$12</definedName>
     <definedName name="docMonthYear" localSheetId="0">'С-29'!$D$11</definedName>
-    <definedName name="docName" localSheetId="0">'С-29'!$A$16</definedName>
-    <definedName name="docObj" localSheetId="0">'С-29'!$A$14</definedName>
+    <definedName name="docName" localSheetId="0">'С-29'!$A$18</definedName>
+    <definedName name="docObj" localSheetId="0">'С-29'!$A$16</definedName>
     <definedName name="forContractor" localSheetId="0">'С-29'!$A$2</definedName>
     <definedName name="signAffirmFio" localSheetId="0">'С-29'!$H$5</definedName>
     <definedName name="signAffirmPic" localSheetId="0">'С-29'!$G$5</definedName>
     <definedName name="signAffirmPos" localSheetId="0">'С-29'!$E$5</definedName>
     <definedName name="signDateAffirm" localSheetId="0">'С-29'!$F$8</definedName>
-    <definedName name="signDateCompose" comment="подпись Дата составления" localSheetId="0">'С-29'!$D$33</definedName>
-    <definedName name="signDatePassToBuh" comment="подпись Дата передачи в бухгалтерию" localSheetId="0">'С-29'!$D$35</definedName>
-    <definedName name="signEngineerPTOfio" localSheetId="0">'С-29'!$F$30</definedName>
-    <definedName name="signEngineerPTOpic" comment="подпись Инженер ПТО" localSheetId="0">'С-29'!$D$30</definedName>
-    <definedName name="signEngineerPTOpos" localSheetId="0">'С-29'!$A$30</definedName>
-    <definedName name="signMOLfio" localSheetId="0">'С-29'!$F$27</definedName>
-    <definedName name="signMOLFioHeader" localSheetId="0">'С-29'!$G$18:$I$18</definedName>
-    <definedName name="signMOLpic" comment="подпись Материально ответственное лицо" localSheetId="0">'С-29'!$D$27</definedName>
-    <definedName name="signMOLPosHeader" comment="в шапке Материально ответственное лицо" localSheetId="0">'С-29'!$D$18:$F$18</definedName>
-    <definedName name="smwCount" localSheetId="0">'С-29'!$F$21</definedName>
-    <definedName name="smwEd" localSheetId="0">'С-29'!$D$21</definedName>
-    <definedName name="smwLab" localSheetId="0">'С-29'!$B$21</definedName>
-    <definedName name="smwName" localSheetId="0">'С-29'!$C$21</definedName>
-    <definedName name="smwNpp" localSheetId="0">'С-29'!$A$21</definedName>
-    <definedName name="smwrPrim" localSheetId="0">'С-29'!$H$21</definedName>
-    <definedName name="smwrTotalCount" localSheetId="0">'С-29'!$G$21</definedName>
-    <definedName name="wrsDivCount" localSheetId="0">'С-29'!$G$26</definedName>
-    <definedName name="wrsEd" localSheetId="0">'С-29'!$D$26</definedName>
-    <definedName name="wrsFCount" localSheetId="0">'С-29'!$F$26</definedName>
-    <definedName name="wrsLab" localSheetId="0">'С-29'!$B$26</definedName>
-    <definedName name="wrsName" localSheetId="0">'С-29'!$C$26</definedName>
-    <definedName name="wrsNpp" localSheetId="0">'С-29'!$A$26</definedName>
-    <definedName name="wrsPrim" localSheetId="0">'С-29'!$I$26</definedName>
-    <definedName name="wrsSCount" localSheetId="0">'С-29'!$E$26</definedName>
-    <definedName name="wrsWriteOff" localSheetId="0">'С-29'!$H$26</definedName>
+    <definedName name="signDateCompose" comment="подпись Дата составления" localSheetId="0">'С-29'!$D$36</definedName>
+    <definedName name="signDatePassToBuh" comment="подпись Дата передачи в бухгалтерию" localSheetId="0">'С-29'!$D$38</definedName>
+    <definedName name="signEngineerPTOfio" localSheetId="0">'С-29'!$F$33</definedName>
+    <definedName name="signEngineerPTOpic" comment="подпись Инженер ПТО" localSheetId="0">'С-29'!$D$33</definedName>
+    <definedName name="signEngineerPTOpos" localSheetId="0">'С-29'!$A$33</definedName>
+    <definedName name="signMOLfio" localSheetId="0">'С-29'!$F$30</definedName>
+    <definedName name="signMOLFioHeader" localSheetId="0">'С-29'!$G$20:$I$20</definedName>
+    <definedName name="signMOLpic" comment="подпись Материально ответственное лицо" localSheetId="0">'С-29'!$D$30</definedName>
+    <definedName name="signMOLPosHeader" comment="в шапке Материально ответственное лицо" localSheetId="0">'С-29'!$D$20:$F$20</definedName>
+    <definedName name="smwCount" localSheetId="0">'С-29'!$F$23</definedName>
+    <definedName name="smwEd" localSheetId="0">'С-29'!$D$23</definedName>
+    <definedName name="smwLab" localSheetId="0">'С-29'!$B$23</definedName>
+    <definedName name="smwName" localSheetId="0">'С-29'!$C$23</definedName>
+    <definedName name="smwNpp" localSheetId="0">'С-29'!$A$23</definedName>
+    <definedName name="smwrPrim" localSheetId="0">'С-29'!$H$23</definedName>
+    <definedName name="smwrTotalCount" localSheetId="0">'С-29'!$G$23</definedName>
+    <definedName name="wrsDivCount" localSheetId="0">'С-29'!$G$28</definedName>
+    <definedName name="wrsEd" localSheetId="0">'С-29'!$D$28</definedName>
+    <definedName name="wrsFCount" localSheetId="0">'С-29'!$F$28</definedName>
+    <definedName name="wrsLab" localSheetId="0">'С-29'!$B$28</definedName>
+    <definedName name="wrsName" localSheetId="0">'С-29'!$C$28</definedName>
+    <definedName name="wrsNpp" localSheetId="0">'С-29'!$A$28</definedName>
+    <definedName name="wrsPrim" localSheetId="0">'С-29'!$I$28</definedName>
+    <definedName name="wrsSCount" localSheetId="0">'С-29'!$E$28</definedName>
+    <definedName name="wrsWriteOff" localSheetId="0">'С-29'!$H$28</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="47">
   <si>
     <t>Форма С-29</t>
   </si>
@@ -104,9 +104,6 @@
     <t>о расходе строительных материалов в сопоставлении с нормами</t>
   </si>
   <si>
-    <t>Объект строительства:</t>
-  </si>
-  <si>
     <t>(наименование объекта строительства)</t>
   </si>
   <si>
@@ -116,9 +113,6 @@
     <t>(наименование части объекта строительства)</t>
   </si>
   <si>
-    <t>Номер и наименование акта:</t>
-  </si>
-  <si>
     <t>Материально ответственное лицо:</t>
   </si>
   <si>
@@ -177,16 +171,58 @@
   </si>
   <si>
     <t>Дата передачи в бухгалтерию</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.000"/>
-  </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial Cyr"/>
@@ -194,26 +230,40 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
       <charset val="204"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
       <charset val="204"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
       <charset val="204"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
       <charset val="204"/>
     </font>
   </fonts>
@@ -357,7 +407,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -369,17 +419,35 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -398,74 +466,59 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -804,8 +857,8 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:I38"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.88671875" style="3" customWidth="1"/>
     <col min="2" max="2" width="12.88671875" style="3" customWidth="1"/>
@@ -813,11 +866,11 @@
     <col min="4" max="5" width="9.6640625" style="3" customWidth="1"/>
     <col min="6" max="7" width="12.6640625" style="3" customWidth="1"/>
     <col min="8" max="8" width="9.6640625" style="3" customWidth="1"/>
-    <col min="9" max="9" width="10.6640625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="20.5546875" style="3" customWidth="1"/>
     <col min="10" max="16384" width="9.109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="2"/>
@@ -827,20 +880,20 @@
       </c>
       <c r="H1" s="1"/>
     </row>
-    <row r="2" spans="1:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="4"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="32" t="s">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
       <c r="E3" s="1" t="s">
         <v>2</v>
       </c>
@@ -848,7 +901,7 @@
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="2"/>
@@ -857,33 +910,33 @@
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="2"/>
-      <c r="E5" s="33"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="35"/>
-      <c r="I5" s="33"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="E5" s="7"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="7"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="2"/>
-      <c r="E6" s="20" t="s">
+      <c r="E6" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="F6" s="20"/>
-      <c r="G6" s="8" t="s">
+      <c r="F6" s="11"/>
+      <c r="G6" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="36" t="s">
+      <c r="H6" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="I6" s="36"/>
-    </row>
-    <row r="7" spans="1:9" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I6" s="13"/>
+    </row>
+    <row r="7" spans="1:9" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="2"/>
@@ -892,7 +945,7 @@
       <c r="H7" s="6"/>
       <c r="I7" s="6"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="2"/>
@@ -905,329 +958,366 @@
       <c r="H8" s="6"/>
       <c r="I8" s="6"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="30" t="s">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="30"/>
-      <c r="C9" s="30"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="30"/>
-      <c r="H9" s="30"/>
-      <c r="I9" s="30"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="30" t="s">
+      <c r="B9" s="14"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="14"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="30"/>
-      <c r="C10" s="30"/>
-      <c r="D10" s="30"/>
-      <c r="E10" s="30"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="30"/>
-      <c r="H10" s="30"/>
-      <c r="I10" s="30"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="14"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="10"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="16"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="11" t="s">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Объект строительства:</t>
+        </is>
+      </c>
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="19"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="13"/>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="14" t="s">
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="17"/>
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="17"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="19"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="19"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="11" t="s">
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="17"/>
+      <c r="I16" s="17"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="19"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="13"/>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="14" t="s">
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="19"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Номер и наименование акта:</t>
+        </is>
+      </c>
+      <c r="B18" s="17"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="17"/>
+      <c r="I18" s="17"/>
+    </row>
+    <row r="19" spans="1:9" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D19" s="21"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-    </row>
-    <row r="17" spans="1:9" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D17" s="15"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D18" s="26"/>
-      <c r="E18" s="26"/>
-      <c r="F18" s="31"/>
-      <c r="G18" s="26"/>
-      <c r="H18" s="26"/>
-      <c r="I18" s="26"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="E19" s="20"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="H19" s="20"/>
-      <c r="I19" s="20"/>
-    </row>
-    <row r="20" spans="1:9" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="23"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="22"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="I22" s="16" t="s">
+      <c r="C21" s="16"/>
+      <c r="D21" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+    </row>
+    <row r="22" spans="1:9" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
+      <c r="I22" s="12"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I24" s="24" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="E25" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="F25" s="28"/>
+      <c r="G25" s="25" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="B23" s="27" t="s">
+      <c r="H25" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="I25" s="25" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="29"/>
+      <c r="B26" s="26"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="F26" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="G26" s="29"/>
+      <c r="H26" s="29"/>
+      <c r="I26" s="29"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="31">
+        <v>1</v>
+      </c>
+      <c r="B27" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="C23" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="D23" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="E23" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="F23" s="29"/>
-      <c r="G23" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="H23" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="I23" s="21" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="22"/>
-      <c r="B24" s="27"/>
-      <c r="C24" s="22"/>
-      <c r="D24" s="22"/>
-      <c r="E24" s="17" t="s">
+      <c r="C27" s="31">
+        <v>3</v>
+      </c>
+      <c r="D27" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="F24" s="17" t="s">
+      <c r="E27" s="31">
+        <v>5</v>
+      </c>
+      <c r="F27" s="31">
+        <v>6</v>
+      </c>
+      <c r="G27" s="31">
+        <v>7</v>
+      </c>
+      <c r="H27" s="31">
+        <v>8</v>
+      </c>
+      <c r="I27" s="31">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="31"/>
+      <c r="B28" s="31"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="31"/>
+      <c r="H28" s="31"/>
+      <c r="I28" s="31"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="1"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="2"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="G24" s="22"/>
-      <c r="H24" s="22"/>
-      <c r="I24" s="22"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="18">
-        <v>1</v>
-      </c>
-      <c r="B25" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="C25" s="18">
-        <v>3</v>
-      </c>
-      <c r="D25" s="18" t="s">
+      <c r="D30" s="32"/>
+      <c r="E30" s="33"/>
+      <c r="F30" s="34"/>
+      <c r="G30" s="22"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D31" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G31" s="11"/>
+    </row>
+    <row r="32" spans="1:7" ht="9.9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="E25" s="18">
-        <v>5</v>
-      </c>
-      <c r="F25" s="18">
-        <v>6</v>
-      </c>
-      <c r="G25" s="18">
-        <v>7</v>
-      </c>
-      <c r="H25" s="18">
-        <v>8</v>
-      </c>
-      <c r="I25" s="18">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" s="18"/>
-      <c r="B26" s="18"/>
-      <c r="C26" s="37"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="38"/>
-      <c r="F26" s="38"/>
-      <c r="G26" s="38"/>
-      <c r="H26" s="38"/>
-      <c r="I26" s="37"/>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" s="3" t="s">
+      <c r="D33" s="32"/>
+      <c r="E33" s="33"/>
+      <c r="F33" s="34"/>
+      <c r="G33" s="22"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D34" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G34" s="11"/>
+    </row>
+    <row r="35" spans="1:7" ht="9.9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D27" s="23"/>
-      <c r="E27" s="24"/>
-      <c r="F27" s="25"/>
-      <c r="G27" s="26"/>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D28" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="G28" s="20"/>
-    </row>
-    <row r="29" spans="1:9" ht="9.9" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" s="19" t="s">
+      <c r="D36" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D30" s="23"/>
-      <c r="E30" s="24"/>
-      <c r="F30" s="25"/>
-      <c r="G30" s="26"/>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D31" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="E31" s="20"/>
-      <c r="F31" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="G31" s="20"/>
-    </row>
-    <row r="32" spans="1:9" ht="9.9" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="3" t="s">
+    </row>
+    <row r="37" spans="1:7" ht="9.9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="9.9" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>32</v>
+      <c r="D38" s="3" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="H25:H26"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A10:I10"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="G21:I21"/>
     <mergeCell ref="A9:I9"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="H5:I5"/>
     <mergeCell ref="E6:F6"/>
     <mergeCell ref="H6:I6"/>
-    <mergeCell ref="A10:I10"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="G23:G24"/>
-    <mergeCell ref="H23:H24"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="F30:G30"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.59055118110236227" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
-  <pageSetup paperSize="9" scale="80" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="74" fitToHeight="0" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>